--- a/Packages/cn.etetet.map/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Base/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.mapmanager/Luban/Config/Base/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.map/Luban/Config/Base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA2794C-B429-8043-AEE7-F487B0E1CF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF8C46C-6B2D-D141-907C-8194113B5914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -127,6 +127,38 @@
   </si>
   <si>
     <t>../../../../cn.etetet.map/Luban/Config/Datas/Map.xlsx</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>ET.UnitConfigCategory</t>
+  </si>
+  <si>
+    <t>UnitConfig</t>
+  </si>
+  <si>
+    <t>UnitConfigCategory</t>
+  </si>
+  <si>
+    <t>MapUnit</t>
+  </si>
+  <si>
+    <t>ET.MapUnitConfigCategory</t>
+  </si>
+  <si>
+    <t>MapUnitConfig</t>
+  </si>
+  <si>
+    <t>MapUnitConfigCategory</t>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.map/Luban/Config/Datas/Unit.xlsx</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>../../../../cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx</t>
     <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +166,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +189,13 @@
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -190,7 +229,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -198,6 +237,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,10 +667,56 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="2"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="B7" s="2"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="2"/>

--- a/Packages/cn.etetet.map/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Base/__tables__.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -116,18 +116,10 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>MapTransferRule</t>
-  </si>
-  <si>
     <t>Map</t>
   </si>
   <si>
-    <t>../../../../cn.etetet.map/Luban/Config/Datas/MapTransferRule.xlsx</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>../../../../cn.etetet.map/Luban/Config/Datas/Map.xlsx</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>Unit</t>
@@ -139,6 +131,9 @@
     <t>UnitConfig</t>
   </si>
   <si>
+    <t>../../../../cn.etetet.map/Luban/Config/Datas/Unit.xlsx</t>
+  </si>
+  <si>
     <t>UnitConfigCategory</t>
   </si>
   <si>
@@ -151,21 +146,17 @@
     <t>MapUnitConfig</t>
   </si>
   <si>
+    <t>../../../../cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx</t>
+  </si>
+  <si>
     <t>MapUnitConfigCategory</t>
-  </si>
-  <si>
-    <t>../../../../cn.etetet.map/Luban/Config/Datas/Unit.xlsx</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>../../../../cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -222,24 +213,24 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -518,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -530,7 +521,7 @@
     <col min="12" max="12" width="47.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -597,7 +588,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -620,68 +611,71 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4">
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="str">
-        <f t="shared" ref="C4" si="0">_xlfn.CONCAT("ET.",B4,"ConfigCategory")</f>
-        <v>ET.MapTransferRuleConfigCategory</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" ref="D4" si="1">_xlfn.CONCAT(B4,"Config")</f>
-        <v>MapTransferRuleConfig</v>
-      </c>
-      <c r="E4" t="b">
+      <c r="C4" s="0" t="str">
+        <f>_xlfn.CONCAT("ET.",B4,"ConfigCategory")</f>
+        <v>ET.MapConfigCategory</v>
+      </c>
+      <c r="D4" s="0" t="str">
+        <f>_xlfn.CONCAT(B4,"Config")</f>
+        <v>MapConfig</v>
+      </c>
+      <c r="E4" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="0" t="str">
+        <f>_xlfn.CONCAT(B4,"ConfigCategory")</f>
+        <v>MapConfigCategory</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L4" t="str">
-        <f t="shared" ref="L4" si="2">_xlfn.CONCAT(B4,"ConfigCategory")</f>
-        <v>MapTransferRuleConfigCategory</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="str">
-        <f>_xlfn.CONCAT("ET.",B5,"ConfigCategory")</f>
-        <v>ET.MapConfigCategory</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" ref="D5" si="3">_xlfn.CONCAT(B5,"Config")</f>
-        <v>MapConfig</v>
-      </c>
-      <c r="E5" t="b">
+      <c r="C5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="str">
-        <f t="shared" ref="L5" si="4">_xlfn.CONCAT(B5,"ConfigCategory")</f>
-        <v>MapConfigCategory</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -689,83 +683,63 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="7">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9">
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15">
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17">
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19">
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20">
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21">
       <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.map/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Base/__tables__.xlsx
@@ -119,7 +119,7 @@
     <t>Map</t>
   </si>
   <si>
-    <t>../../../../cn.etetet.map/Luban/Config/Datas/Map.xlsx</t>
+    <t>Packages/cn.etetet.map/Luban/Config/Datas/Map.xlsx</t>
   </si>
   <si>
     <t>Unit</t>
@@ -131,7 +131,7 @@
     <t>UnitConfig</t>
   </si>
   <si>
-    <t>../../../../cn.etetet.map/Luban/Config/Datas/Unit.xlsx</t>
+    <t>Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx</t>
   </si>
   <si>
     <t>UnitConfigCategory</t>
@@ -146,7 +146,7 @@
     <t>MapUnitConfig</t>
   </si>
   <si>
-    <t>../../../../cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx</t>
+    <t>Packages/cn.etetet.map/Luban/Config/Datas/MapUnit.xlsx</t>
   </si>
   <si>
     <t>MapUnitConfigCategory</t>
